--- a/Common_Data/meiv2.xlsx
+++ b/Common_Data/meiv2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JohnMatthew/Downloads/Thorne_figures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JohnMatthew/Downloads/Thorne_15_codefigurestats/Common_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15831A43-318E-354F-8B12-46F87266227F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E774FA20-6A2C-264E-9183-82EDF2C24A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="2700" windowWidth="27640" windowHeight="16940" activeTab="2" xr2:uid="{EB692CA6-D399-914A-8C62-CB1A49C58546}"/>
+    <workbookView xWindow="13340" yWindow="2360" windowWidth="27640" windowHeight="16940" activeTab="2" xr2:uid="{EB692CA6-D399-914A-8C62-CB1A49C58546}"/>
   </bookViews>
   <sheets>
     <sheet name="meiv2" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
   <si>
     <t>YEAR</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>strongly correlated!</t>
+  </si>
+  <si>
+    <t>AAA</t>
   </si>
 </sst>
 </file>
@@ -534,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FD91B4-DEC9-7E46-9CD5-4BE5EBD6D1BA}">
-  <dimension ref="A1:U51"/>
+  <dimension ref="A1:Z51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
@@ -673,7 +676,7 @@
         <v>-0.12</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N46" si="0">AVERAGE(B3:M3)</f>
+        <f t="shared" ref="N3:N48" si="0">AVERAGE(B3:M3)</f>
         <v>0.24000000000000002</v>
       </c>
       <c r="P3" t="s">
@@ -2231,7 +2234,7 @@
         <v>-2.4999999999999967E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2010</v>
       </c>
@@ -2295,7 +2298,7 @@
         <v>1.8378643243118206E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2011</v>
       </c>
@@ -2355,7 +2358,7 @@
         <v>5.5162485052255281E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2012</v>
       </c>
@@ -2415,7 +2418,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2013</v>
       </c>
@@ -2475,7 +2478,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2014</v>
       </c>
@@ -2535,7 +2538,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>2015</v>
       </c>
@@ -2584,7 +2587,7 @@
         <v>0.87790293122781748</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>2016</v>
       </c>
@@ -2629,7 +2632,7 @@
         <v>0.45999999999999991</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>2017</v>
       </c>
@@ -2674,7 +2677,7 @@
         <v>-0.47666666666666663</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>2018</v>
       </c>
@@ -2719,7 +2722,7 @@
         <v>-0.25166666666666665</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>2019</v>
       </c>
@@ -2764,7 +2767,7 @@
         <v>0.34583333333333338</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>2020</v>
       </c>
@@ -2809,7 +2812,7 @@
         <v>-0.57583333333333331</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>2021</v>
       </c>
@@ -2854,7 +2857,7 @@
         <v>-1.1816666666666666</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>2022</v>
       </c>
@@ -2899,7 +2902,7 @@
         <v>-1.5525000000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>2023</v>
       </c>
@@ -2943,11 +2946,11 @@
         <f t="shared" si="0"/>
         <v>0.11916666666666664</v>
       </c>
-      <c r="P46" t="s">
+      <c r="Z46" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>2024</v>
       </c>
@@ -2975,78 +2978,142 @@
       <c r="I47">
         <v>-0.73</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47">
+        <v>-0.65</v>
+      </c>
+      <c r="K47">
+        <v>-0.51</v>
+      </c>
+      <c r="L47">
+        <v>-0.68</v>
+      </c>
+      <c r="M47">
+        <v>-0.91</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="0"/>
+        <v>-0.15083333333333335</v>
+      </c>
+      <c r="T47" s="1">
         <f>I47*Q3+H47*R3+G47*S3+F47*T3+U3</f>
         <v>-0.67797571599399642</v>
       </c>
-      <c r="K47" s="1">
+      <c r="U47" s="1">
         <f>I47*Q13+H47*R13+G47*S13+F47*T13+U13</f>
         <v>-0.68451514021807291</v>
       </c>
-      <c r="L47" s="1">
+      <c r="V47" s="1">
         <f>I47*Q23+H47*R23+G47*S23+F47*T23+U23</f>
         <v>-0.65704550123881034</v>
       </c>
-      <c r="M47" s="1">
+      <c r="W47" s="1">
         <f>I47*Q33+H47*R33+G47*S33+F47*T33+U33</f>
         <v>-0.62299748826780832</v>
       </c>
-      <c r="N47" cm="1">
-        <f t="array" ref="N47">SUM(B47:M47*B48:M48)/SUM(B48:M48)</f>
-        <v>-0.12653834620163959</v>
-      </c>
-      <c r="O47">
-        <f>AVERAGE(B47:M47)</f>
-        <v>-0.14187782047655731</v>
-      </c>
-      <c r="P47">
+      <c r="X47" cm="1">
+        <f t="array" ref="X47">SUM(B47:W47*B48:W48)/SUM(B48:W48)</f>
+        <v>-3.6941895130223626E-2</v>
+      </c>
+      <c r="Y47">
+        <f>AVERAGE(B47:W47)</f>
+        <v>-0.27078630465011894</v>
+      </c>
+      <c r="Z47">
         <f>AVERAGE(B47:I47)</f>
         <v>0.11750000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>2025</v>
+      </c>
       <c r="B48">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>-0.83</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>-0.68</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>-0.38</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>-0.36</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>-1.17</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>-1.22</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>-0.87</v>
       </c>
       <c r="J48">
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="K48">
+        <v>-1.19</v>
+      </c>
+      <c r="L48">
+        <v>-1.06</v>
+      </c>
+      <c r="M48">
+        <v>-0.77</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="0"/>
+        <v>-0.88750000000000007</v>
+      </c>
+      <c r="T48">
         <f>Q8</f>
         <v>0.96322645677157459</v>
       </c>
-      <c r="K48">
+      <c r="U48">
         <f>Q18</f>
         <v>0.91056982095588479</v>
       </c>
-      <c r="L48">
+      <c r="V48">
         <f>Q28</f>
         <v>0.8995692815176668</v>
       </c>
-      <c r="M48">
+      <c r="W48">
         <f>Q38</f>
         <v>0.87790293122781748</v>
       </c>
     </row>
-    <row r="51" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>2026</v>
+      </c>
+      <c r="B49">
+        <v>-0.76</v>
+      </c>
+      <c r="C49">
+        <v>-0.95</v>
+      </c>
+      <c r="D49">
+        <v>-1.03</v>
+      </c>
+      <c r="E49">
+        <v>-0.64</v>
+      </c>
+      <c r="F49">
+        <v>0.27</v>
+      </c>
+      <c r="G49">
+        <v>1.52</v>
+      </c>
+      <c r="H49">
+        <v>2.41</v>
+      </c>
+      <c r="I49">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K51" t="s">
         <v>17</v>
       </c>
@@ -9298,7 +9365,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFD98612-A8FA-F640-8F85-794EE2C963E9}">
-  <dimension ref="A1:N154"/>
+  <dimension ref="A1:N157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
@@ -10237,7 +10304,7 @@
         <v>-0.63800000000000001</v>
       </c>
       <c r="N21">
-        <f t="shared" si="0"/>
+        <f>(SUM(B21:I21)+SUM(J20:M20))/12</f>
         <v>-1.508</v>
       </c>
     </row>
@@ -16224,6 +16291,163 @@
       <c r="N154">
         <f>(SUM(B154:I154)+SUM(J153:M153))/12</f>
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <f>meiv2!A47</f>
+        <v>2024</v>
+      </c>
+      <c r="B155">
+        <f>meiv2!B47</f>
+        <v>0.7</v>
+      </c>
+      <c r="C155">
+        <f>meiv2!C47</f>
+        <v>0.68</v>
+      </c>
+      <c r="D155">
+        <f>meiv2!D47</f>
+        <v>0.78</v>
+      </c>
+      <c r="E155">
+        <f>meiv2!E47</f>
+        <v>0.34</v>
+      </c>
+      <c r="F155">
+        <f>meiv2!F47</f>
+        <v>0.12</v>
+      </c>
+      <c r="G155">
+        <f>meiv2!G47</f>
+        <v>-0.23</v>
+      </c>
+      <c r="H155">
+        <f>meiv2!H47</f>
+        <v>-0.72</v>
+      </c>
+      <c r="I155">
+        <f>meiv2!I47</f>
+        <v>-0.73</v>
+      </c>
+      <c r="J155">
+        <f>meiv2!J47</f>
+        <v>-0.65</v>
+      </c>
+      <c r="K155">
+        <f>meiv2!K47</f>
+        <v>-0.51</v>
+      </c>
+      <c r="L155">
+        <f>meiv2!L47</f>
+        <v>-0.68</v>
+      </c>
+      <c r="M155">
+        <f>meiv2!M47</f>
+        <v>-0.91</v>
+      </c>
+      <c r="N155">
+        <f t="shared" ref="N155:N156" si="3">(SUM(B155:I155)+SUM(J154:M154))/12</f>
+        <v>0.34500000000000003</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <f>meiv2!A48</f>
+        <v>2025</v>
+      </c>
+      <c r="B156">
+        <f>meiv2!B48</f>
+        <v>-1</v>
+      </c>
+      <c r="C156">
+        <f>meiv2!C48</f>
+        <v>-0.83</v>
+      </c>
+      <c r="D156">
+        <f>meiv2!D48</f>
+        <v>-0.68</v>
+      </c>
+      <c r="E156">
+        <f>meiv2!E48</f>
+        <v>-0.38</v>
+      </c>
+      <c r="F156">
+        <f>meiv2!F48</f>
+        <v>-0.36</v>
+      </c>
+      <c r="G156">
+        <f>meiv2!G48</f>
+        <v>-1.17</v>
+      </c>
+      <c r="H156">
+        <f>meiv2!H48</f>
+        <v>-1.22</v>
+      </c>
+      <c r="I156">
+        <f>meiv2!I48</f>
+        <v>-0.87</v>
+      </c>
+      <c r="J156">
+        <f>meiv2!J48</f>
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="K156">
+        <f>meiv2!K48</f>
+        <v>-1.19</v>
+      </c>
+      <c r="L156">
+        <f>meiv2!L48</f>
+        <v>-1.06</v>
+      </c>
+      <c r="M156">
+        <f>meiv2!M48</f>
+        <v>-0.77</v>
+      </c>
+      <c r="N156">
+        <f t="shared" si="3"/>
+        <v>-0.77166666666666661</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <f>meiv2!A49</f>
+        <v>2026</v>
+      </c>
+      <c r="B157">
+        <f>meiv2!B49</f>
+        <v>-0.76</v>
+      </c>
+      <c r="C157">
+        <f>meiv2!C49</f>
+        <v>-0.95</v>
+      </c>
+      <c r="D157">
+        <f>meiv2!D49</f>
+        <v>-1.03</v>
+      </c>
+      <c r="E157">
+        <f>meiv2!E49</f>
+        <v>-0.64</v>
+      </c>
+      <c r="F157">
+        <f>meiv2!F49</f>
+        <v>0.27</v>
+      </c>
+      <c r="G157">
+        <f>meiv2!G49</f>
+        <v>1.52</v>
+      </c>
+      <c r="H157">
+        <f>meiv2!H49</f>
+        <v>2.41</v>
+      </c>
+      <c r="I157">
+        <f>meiv2!I49</f>
+        <v>2.54</v>
+      </c>
+      <c r="J157" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
